--- a/product Tester/templates/test-cases-ctn.xlsx
+++ b/product Tester/templates/test-cases-ctn.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9120"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>ID</t>
   </si>
@@ -47,152 +47,45 @@
     <t>TC-01</t>
   </si>
   <si>
-    <t>Open Website</t>
+    <t>Hiển thị nút</t>
   </si>
   <si>
     <t>Check if the website can be opened</t>
   </si>
   <si>
-    <t>1. Enter URL: https://ctnone.github.io/web-profile/
-2. Press Enter</t>
-  </si>
-  <si>
-    <t>The website loads and shows the Home page</t>
+    <t xml:space="preserve">1. Enter into website </t>
+  </si>
+  <si>
+    <t>Dowload button can be see at the top of menu</t>
   </si>
   <si>
     <t>TC-02</t>
   </si>
   <si>
-    <t>Avatar Image</t>
-  </si>
-  <si>
-    <t>Check if the profile picture is visible</t>
-  </si>
-  <si>
-    <t>1. Look at the Profile/Hero section</t>
-  </si>
-  <si>
-    <t>The avatar image is displayed clearly (not broken)</t>
-  </si>
-  <si>
-    <t>TC-03</t>
-  </si>
-  <si>
-    <t>Menu Click</t>
-  </si>
-  <si>
-    <t>Check if the Menu buttons work</t>
-  </si>
-  <si>
-    <t>1. Click on "About" or "Dự án" in the menu</t>
-  </si>
-  <si>
-    <t>The page scrolls down to the selected section</t>
-  </si>
-  <si>
-    <t>TC-04</t>
-  </si>
-  <si>
-    <t>Title Text</t>
-  </si>
-  <si>
-    <t>Check the main heading (Name/Job)</t>
-  </si>
-  <si>
-    <t>1. Read the main text on the Home page</t>
-  </si>
-  <si>
-    <t>Your name (e.g., "CTN") and job title are correct</t>
-  </si>
-  <si>
-    <t>TC-05</t>
-  </si>
-  <si>
-    <t>GitHub Link</t>
-  </si>
-  <si>
-    <t>Check the GitHub icon/link</t>
-  </si>
-  <si>
-    <t>1. Click on the GitHub icon</t>
-  </si>
-  <si>
-    <t>A new tab opens your GitHub profile page</t>
-  </si>
-  <si>
-    <t>TC-06</t>
-  </si>
-  <si>
-    <t>LinkedIn Link</t>
-  </si>
-  <si>
-    <t>Check the LinkedIn icon/link</t>
-  </si>
-  <si>
-    <t>1. Click on the LinkedIn icon</t>
-  </si>
-  <si>
-    <t>A new tab opens your LinkedIn profile page</t>
-  </si>
-  <si>
-    <t>TC-07</t>
-  </si>
-  <si>
-    <t>Facebook Link</t>
-  </si>
-  <si>
-    <t>Check the Facebook icon/link</t>
-  </si>
-  <si>
-    <t>1. Click on the Facebook icon</t>
-  </si>
-  <si>
-    <t>A new tab opens your Facebook profile page</t>
-  </si>
-  <si>
-    <t>TC-08</t>
-  </si>
-  <si>
-    <t>Scroll Down</t>
-  </si>
-  <si>
-    <t>Check if the user can scroll</t>
-  </si>
-  <si>
-    <t>1. Use the mouse wheel to scroll down</t>
-  </si>
-  <si>
-    <t>The page moves smoothly to the bottom</t>
-  </si>
-  <si>
-    <t>TC-09</t>
-  </si>
-  <si>
-    <t>Contact Email</t>
-  </si>
-  <si>
-    <t>Check if the email link works</t>
-  </si>
-  <si>
-    <t>1. Find and click on the email address/icon</t>
-  </si>
-  <si>
-    <t>The mail app (Outlook/Gmail) opens to compose a new mail</t>
-  </si>
-  <si>
-    <t>TC-10</t>
-  </si>
-  <si>
-    <t>Mobile View</t>
-  </si>
-  <si>
-    <t>Check the website on a phone</t>
-  </si>
-  <si>
-    <t>1. Open the link on a smartphone browser</t>
-  </si>
-  <si>
-    <t>The text and images fit the screen (no horizontal scrolling)</t>
+    <t>Check icon button</t>
+  </si>
+  <si>
+    <t>Check if the dowload button can be changes</t>
+  </si>
+  <si>
+    <t>1. Open URL website
+2. move the mouse to dowload button</t>
+  </si>
+  <si>
+    <t>the button changes the color and effect (shadow)</t>
+  </si>
+  <si>
+    <t>TC-3</t>
+  </si>
+  <si>
+    <t>Check if the dowload button can be changes and dowload</t>
+  </si>
+  <si>
+    <t>1. move the mouse to dowload button
+2. click button dowload</t>
+  </si>
+  <si>
+    <t>a website can be open</t>
   </si>
 </sst>
 </file>
@@ -1291,7 +1184,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="2" max="3" width="27.3" customWidth="1"/>
+    <col min="2" max="2" width="19.9" customWidth="1"/>
+    <col min="3" max="3" width="33.5" customWidth="1"/>
     <col min="4" max="4" width="45.9" customWidth="1"/>
     <col min="5" max="5" width="55.6" customWidth="1"/>
     <col min="6" max="6" width="27.3" customWidth="1"/>
@@ -1355,141 +1249,71 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" ht="27.6" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
     </row>
     <row r="6" ht="29.1" customHeight="1" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" ht="17.85" customHeight="1" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" ht="27.6" customHeight="1" spans="1:5">
-      <c r="A10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" ht="17.1" customHeight="1" spans="1:5">
       <c r="A13" s="2"/>
